--- a/Piaui/2026/Julho/ResultadosTRI_3EM_LP/Simulado_III/ResumoTheta_3EM_LP_S3.xlsx
+++ b/Piaui/2026/Julho/ResultadosTRI_3EM_LP/Simulado_III/ResumoTheta_3EM_LP_S3.xlsx
@@ -389,7 +389,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>235.392621122818</v>
+        <v>235.387336450139</v>
       </c>
     </row>
     <row r="3">
@@ -397,7 +397,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>75.1814205632598</v>
+        <v>75.1417569080187</v>
       </c>
     </row>
     <row r="4">
@@ -405,7 +405,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>31.9387329155205</v>
+        <v>31.9225995931755</v>
       </c>
     </row>
     <row r="5">
@@ -413,7 +413,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>77.7315231734672</v>
+        <v>77.9596738105589</v>
       </c>
     </row>
     <row r="6">
@@ -421,7 +421,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>174.81115091138</v>
+        <v>174.850599632707</v>
       </c>
     </row>
     <row r="7">
@@ -429,7 +429,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>241.48897856486</v>
+        <v>241.446263562425</v>
       </c>
     </row>
     <row r="8">
@@ -437,7 +437,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>292.949611944604</v>
+        <v>292.816591828231</v>
       </c>
     </row>
     <row r="9">
@@ -445,7 +445,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>444.371488219746</v>
+        <v>428.68094805078</v>
       </c>
     </row>
     <row r="10">
@@ -453,7 +453,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.0723188169594239</v>
+        <v>-0.0733173112272871</v>
       </c>
     </row>
     <row r="11">
@@ -461,7 +461,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="n">
-        <v>2.18224193795082</v>
+        <v>2.18013133608533</v>
       </c>
     </row>
   </sheetData>
